--- a/docs/payhome_sales.xlsx
+++ b/docs/payhome_sales.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工務店ヒアリング管理" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ペルソナカード" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方ガイド" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ステップメール設計" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ステップメール配信管理" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +58,30 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002E4057"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00E8740C"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,8 +93,13 @@
         <fgColor rgb="00E8740C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -92,11 +121,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5D8DC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D8DC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -112,6 +155,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3201,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3428,10 +3486,1143 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>ステップメール設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>工務店向けナーチャリングメールの設計書。6段階のステップメールの件名・本文・KPI目標を管理。全メール末尾に配信停止URLが含まれています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>ステップメール配信管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>各企業へのステップメール配信状況を管理。送信日・開封・クリックをStep別に記録。2回連続未開封で休眠リストへ。ステータスはプルダウンで選択。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8740C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ステップメール設計（工務店向けナーチャリング）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>戦略概要</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>目的：一度接点を持った工務店に対し、段階的に価値を伝え、掲載契約に導く。
+配信フロー：初回接触 → Step1(当日) → Step2(3日後) → Step3(7日後) → Step4(14日後) → Step5(21日後) → Step6(30日後)
+離脱時：Step3以降で未開封が2回連続 → 休眠リストへ移動。3ヶ月後に再アプローチ。
+重要：全メール末尾に配信停止URLを必ず挿入すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>ステップメール一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>送信タイミング</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>KPI目標（開封率）</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>KPI目標（クリック率）</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>接触当日</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>お打ち合わせ（お問い合わせ）のお礼｜ぺいほーむ</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>関係構築・好印象</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>提案資料（PDF）の確認</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>初回は温度が高い。即日送信が重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>3日後</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>【データ公開】ぺいほーむの視聴者データをお送りします</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>数字で興味喚起</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>データレポートページ閲覧</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>具体的な数字で「使える」と思わせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>7日後</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>【事例紹介】ぺいほーむ掲載で反響を得た工務店様の声</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>社会的証明</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>事例ページ閲覧</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>同業他社の成功事例が最も刺さる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>14日後</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>【市場動向】九州の平屋市場、最新トレンドをお届けします</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>業界知見の提供</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>記事ページ閲覧</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>売り込みではなく情報提供の姿勢</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>21日後</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>【期間限定】ぺいほーむ無料トライアルのご案内</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>具体的な提案</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>トライアル申込ページ</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>無料で試せるハードルの低さを訴求</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>30日後</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>【最終ご案内】ぺいほーむ掲載のご検討はいかがでしょうか</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>最後の後押し</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>個別相談予約フォーム</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>反応なければ休眠リストへ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>メール本文テンプレート</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="350" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>お打ち合わせ（お問い合わせ）のお礼｜ぺいほーむ</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>{{company_name}} {{contact_name}}様
+お忙しい中、{{contact_type}}いただき誠にありがとうございます。
+鹿児島発・九州特化の平屋専門住宅メディア「ぺいほーむ」の{{sender_name}}です。
+改めまして、ぺいほーむのサービス概要をお送りいたします。
+【ぺいほーむの特徴】
+・YouTube登録者42,000人超の平屋専門チャンネルと連動
+・九州で平屋を検討中のユーザーに直接リーチ可能
+・動画撮影からWeb掲載、反響送客までワンストップで対応
+▼ 提案資料はこちらからご確認いただけます
+{{proposal_url}}
+ご不明な点やご質問がございましたら、お気軽にご返信ください。
+今後ともどうぞよろしくお願いいたします。
+{{sender_signature}}
+---
+本メールは、過去にぺいほーむにお問い合わせいただいた企業様にお送りしています。
+配信停止をご希望の場合は下記URLよりお手続きください。
+https://payhome.jp/unsubscribe?token={{unsubscribe_token}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="350" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>【データ公開】ぺいほーむの視聴者データをお送りします</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>{{company_name}} {{contact_name}}様
+お世話になっております。ぺいほーむの{{sender_name}}です。
+先日はお時間をいただきありがとうございました。
+本日は、ぺいほーむの視聴者データを共有させていただきます。
+【ぺいほーむ視聴者の特徴】
+・月間再生回数：150,000回以上
+・視聴者の年齢層：30代～50代が72%
+・男女比：男恧58% / 女恧42%
+・新規視聴者率：毎月65%以上が新規
+・視聴地域：九州エリアが全体の48%
+▼ 詳細なデータレポートはこちら
+{{data_report_url}}
+このデータが御社のマーケティングにどう活かせるか、
+具体的にご説明する機会をいただけましたら幸いです。
+{{sender_signature}}
+---
+本メールは、過去にぺいほーむにお問い合わせいただいた企業様にお送りしています。
+配信停止をご希望の場合は下記URLよりお手続きください。
+https://payhome.jp/unsubscribe?token={{unsubscribe_token}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="350" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>【事例紹介】ぺいほーむ掲載で反響を得た工務店様の声</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>{{company_name}} {{contact_name}}様
+お世話になっております。ぺいほーむの{{sender_name}}です。
+本日は、ぺいほーむをご活用いただいている工務店様の事例をご紹介します。
+【掲載事例】
+▼ A工務店様（鹿児島市）
+・掲載開始から3ヶ月で月間問い合わせ数が2.3倍に
+・YouTubeルームツアー動画の平均再生回数：12,000回
+・「動画を見て来ました」というお客様が増えた
+▼ B工務店様（熊本市）
+・SNS運用を含むトータル支援で認知度が向上
+・見学会の予約率が1.8倍に改善
+・Web経由の成約が全体の35%を占めるように
+▼ 詳しい事例はこちら
+{{case_study_url}}
+御社でも同様の成果を出せる可能性がございます。
+ぜひ一度、具体的なプランをご相談させてください。
+{{sender_signature}}
+---
+本メールは、過去にぺいほーむにお問い合わせいただいた企業様にお送りしています。
+配信停止をご希望の場合は下記URLよりお手続きください。
+https://payhome.jp/unsubscribe?token={{unsubscribe_token}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="350" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>【市場動向】九州の平屋市場、最新トレンドをお届けします</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>{{company_name}} {{contact_name}}様
+お世話になっております。ぺいほーむの{{sender_name}}です。
+本日は、私たちが日々の取材・動画制作を通じて把握している
+九州の平屋市場の最新トレンドをお届けします。
+【2026年 九州平屋市場の注目トレンド】
+1. 20代～30代の平屋検討者が前年比1.4倍に増加
+2. 「老後も安心」から「今の暮らしを楽しむ」へ検討理由がシフト
+3. 回遊動線・中庭のある平屋の検索ニーズが急増
+4. SNSでの情報収集が主流に（YouTube・Instagram）
+5. 坪単価55～75万円帯の平屋が最も需要が高い
+▼ 詳しい市場分析レポートはこちら
+{{market_report_url}}
+こうした市場動向を踏まえた集客戦略について、
+御社に合わせたご提案が可能です。
+{{sender_signature}}
+---
+本メールは、過去にぺいほーむにお問い合わせいただいた企業様にお送りしています。
+配信停止をご希望の場合は下記URLよりお手続きください。
+https://payhome.jp/unsubscribe?token={{unsubscribe_token}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="350" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>【期間限定】ぺいほーむ無料トライアルのご案内</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>{{company_name}} {{contact_name}}様
+お世話になっております。ぺいほーむの{{sender_name}}です。
+これまでのメールをご覧いただきありがとうございます。
+本日は、ぺいほーむの無料トライアルプランのご案内です。
+【無料トライアルの内容（1ヶ月間）】
+・ぺいほーむへの工務店ページ掲載
+・基本情報 + 施工事例3件の掲載
+・期間中に発生した反響（資料請求・見学会予約）の送客
+・掲載ページのアクセスレポート
+【トライアル開始までの流れ】
+1. 下記フォームからお申し込み（所要時間：2分）
+2. 弊社から掲載情報のヒアリング（30分程度）
+3. 掲載ページ作成・公開（最短3営業日）
+▼ 無料トライアルのお申し込みはこちら
+{{trial_url}}
+※ トライアル期間中の費用は一切かかりません。
+※ トライアル後の自動更新はございません。
+ご不明な点がございましたらお気軽にご連絡ください。
+{{sender_signature}}
+---
+本メールは、過去にぺいほーむにお問い合わせいただいた企業様にお送りしています。
+配信停止をご希望の場合は下記URLよりお手続きください。
+https://payhome.jp/unsubscribe?token={{unsubscribe_token}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="350" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>【最終ご案内】ぺいほーむ掲載のご検討はいかがでしょうか</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>{{company_name}} {{contact_name}}様
+お世話になっております。ぺいほーむの{{sender_name}}です。
+これまで数回にわたり、ぺいほーむのサービスについて
+ご案内させていただきました。
+改めまして、御社にとってぺいほーむが
+お役に立てるポイントを整理いたします。
+【御社へのご提案ポイント】
+・九州で平屋を検討中のユーザーへ直接リーチ
+・YouTube動画による高い訴求力（平均再生12,000回）
+・初期費用を抑えたプランからスタート可能
+・反響課金型なので成果が出なければコストゼロ
+もし現時点でご検討が難しい場合でも、
+将来的にご興味をお持ちいただけた際にはぜひお声がけください。
+▼ 個別相談のご予約はこちら
+{{consultation_url}}
+今後とも、九州の住宅業界の発展に貢献できるよう
+努めてまいります。引き続きどうぞよろしくお願いいたします。
+{{sender_signature}}
+---
+本メールは、過去にぺいほーむにお問い合わせいただいた企業様にお送りしています。
+配信停止をご希望の場合は下記URLよりお手続きください。
+https://payhome.jp/unsubscribe?token={{unsubscribe_token}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8740C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ステップメール配信管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>企業名</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>担当者名</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>メールアドレス</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>初回接触日</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>接触方法</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Step1
+送信日</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Step1
+開封</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Step1
+クリック</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Step2
+送信日</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>Step2
+開封</t>
+        </is>
+      </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>Step2
+クリック</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
+        <is>
+          <t>Step3
+送信日</t>
+        </is>
+      </c>
+      <c r="N3" s="14" t="inlineStr">
+        <is>
+          <t>Step3
+開封</t>
+        </is>
+      </c>
+      <c r="O3" s="14" t="inlineStr">
+        <is>
+          <t>Step3
+クリック</t>
+        </is>
+      </c>
+      <c r="P3" s="14" t="inlineStr">
+        <is>
+          <t>Step4
+送信日</t>
+        </is>
+      </c>
+      <c r="Q3" s="14" t="inlineStr">
+        <is>
+          <t>Step4
+開封</t>
+        </is>
+      </c>
+      <c r="R3" s="14" t="inlineStr">
+        <is>
+          <t>Step4
+クリック</t>
+        </is>
+      </c>
+      <c r="S3" s="14" t="inlineStr">
+        <is>
+          <t>Step5
+送信日</t>
+        </is>
+      </c>
+      <c r="T3" s="14" t="inlineStr">
+        <is>
+          <t>Step5
+開封</t>
+        </is>
+      </c>
+      <c r="U3" s="14" t="inlineStr">
+        <is>
+          <t>Step5
+クリック</t>
+        </is>
+      </c>
+      <c r="V3" s="14" t="inlineStr">
+        <is>
+          <t>Step6
+送信日</t>
+        </is>
+      </c>
+      <c r="W3" s="14" t="inlineStr">
+        <is>
+          <t>Step6
+開封</t>
+        </is>
+      </c>
+      <c r="X3" s="14" t="inlineStr">
+        <is>
+          <t>Step6
+クリック</t>
+        </is>
+      </c>
+      <c r="Y3" s="14" t="inlineStr">
+        <is>
+          <t>現在のStep</t>
+        </is>
+      </c>
+      <c r="Z3" s="14" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="AA3" s="14" t="inlineStr">
+        <is>
+          <t>返信有無</t>
+        </is>
+      </c>
+      <c r="AB3" s="14" t="inlineStr">
+        <is>
+          <t>アポ取得</t>
+        </is>
+      </c>
+      <c r="AC3" s="14" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>SM-001</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>〇〇工務店</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>田中太郎</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>tanaka@example.com</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>展示会</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr"/>
+      <c r="H4" s="15" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
+      <c r="J4" s="15" t="inlineStr"/>
+      <c r="K4" s="15" t="inlineStr"/>
+      <c r="L4" s="15" t="inlineStr"/>
+      <c r="M4" s="15" t="inlineStr"/>
+      <c r="N4" s="15" t="inlineStr"/>
+      <c r="O4" s="15" t="inlineStr"/>
+      <c r="P4" s="15" t="inlineStr"/>
+      <c r="Q4" s="15" t="inlineStr"/>
+      <c r="R4" s="15" t="inlineStr"/>
+      <c r="S4" s="15" t="inlineStr"/>
+      <c r="T4" s="15" t="inlineStr"/>
+      <c r="U4" s="15" t="inlineStr"/>
+      <c r="V4" s="15" t="inlineStr"/>
+      <c r="W4" s="15" t="inlineStr"/>
+      <c r="X4" s="15" t="inlineStr"/>
+      <c r="Y4" s="15" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="Z4" s="15" t="inlineStr">
+        <is>
+          <t>配信中</t>
+        </is>
+      </c>
+      <c r="AA4" s="15" t="inlineStr"/>
+      <c r="AB4" s="15" t="inlineStr"/>
+      <c r="AC4" s="15" t="inlineStr">
+        <is>
+          <t>初回提案済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>SM-002</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>△△ハウス</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>鈴木一郎</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>suzuki@example.com</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>テレアポ</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr"/>
+      <c r="N5" s="15" t="inlineStr"/>
+      <c r="O5" s="15" t="inlineStr"/>
+      <c r="P5" s="15" t="inlineStr"/>
+      <c r="Q5" s="15" t="inlineStr"/>
+      <c r="R5" s="15" t="inlineStr"/>
+      <c r="S5" s="15" t="inlineStr"/>
+      <c r="T5" s="15" t="inlineStr"/>
+      <c r="U5" s="15" t="inlineStr"/>
+      <c r="V5" s="15" t="inlineStr"/>
+      <c r="W5" s="15" t="inlineStr"/>
+      <c r="X5" s="15" t="inlineStr"/>
+      <c r="Y5" s="15" t="inlineStr">
+        <is>
+          <t>Step 3待ち</t>
+        </is>
+      </c>
+      <c r="Z5" s="15" t="inlineStr">
+        <is>
+          <t>配信中</t>
+        </is>
+      </c>
+      <c r="AA5" s="15" t="inlineStr"/>
+      <c r="AB5" s="15" t="inlineStr"/>
+      <c r="AC5" s="15" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>SM-003</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>□□建設</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>佐藤花子</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>sato@example.com</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="Q6" s="15" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="R6" s="15" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="S6" s="15" t="inlineStr"/>
+      <c r="T6" s="15" t="inlineStr"/>
+      <c r="U6" s="15" t="inlineStr"/>
+      <c r="V6" s="15" t="inlineStr"/>
+      <c r="W6" s="15" t="inlineStr"/>
+      <c r="X6" s="15" t="inlineStr"/>
+      <c r="Y6" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z6" s="15" t="inlineStr">
+        <is>
+          <t>休眠</t>
+        </is>
+      </c>
+      <c r="AA6" s="15" t="inlineStr"/>
+      <c r="AB6" s="15" t="inlineStr"/>
+      <c r="AC6" s="15" t="inlineStr">
+        <is>
+          <t>Step3,4連続未開封→休眠</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AC1"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="Z4:Z100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"配信中,配信完了,休眠,契約済み,配信停止,対象外"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H4:H100 I4:I100 K4:K100 L4:L100 N4:N100 O4:O100 Q4:Q100 R4:R100 T4:T100 U4:U100 W4:W100 X4:X100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA4:AA100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"あり,なし"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB4:AB100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"済,未"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"展示会,テレアポ,メール,紹介,YouTube問い合わせ,Web問い合わせ,SNS,その他"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>